--- a/results/안산도금단지/안산도금단지_valid_Informer_(36,32)_peak_weight_first_window.xlsx
+++ b/results/안산도금단지/안산도금단지_valid_Informer_(36,32)_peak_weight_first_window.xlsx
@@ -465,7 +465,7 @@
         <v>399.1200256347656</v>
       </c>
       <c r="D2" t="n">
-        <v>356.7833557128906</v>
+        <v>426.6586303710938</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>419.5199890136719</v>
       </c>
       <c r="D3" t="n">
-        <v>356.7826538085938</v>
+        <v>436.6207580566406</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         <v>427.6800842285156</v>
       </c>
       <c r="D4" t="n">
-        <v>335.3814697265625</v>
+        <v>440.994384765625</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>413.0401000976562</v>
       </c>
       <c r="D5" t="n">
-        <v>335.3818054199219</v>
+        <v>443.6155395507812</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         <v>380.6399230957031</v>
       </c>
       <c r="D6" t="n">
-        <v>335.3814697265625</v>
+        <v>442.4051208496094</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +535,7 @@
         <v>389.2800598144531</v>
       </c>
       <c r="D7" t="n">
-        <v>258.1430358886719</v>
+        <v>439.6309814453125</v>
       </c>
     </row>
     <row r="8">
@@ -549,7 +549,7 @@
         <v>379.6799011230469</v>
       </c>
       <c r="D8" t="n">
-        <v>335.3806762695312</v>
+        <v>435.8176879882812</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>373.679931640625</v>
       </c>
       <c r="D9" t="n">
-        <v>281.0340576171875</v>
+        <v>429.4970397949219</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         <v>379.9199523925781</v>
       </c>
       <c r="D10" t="n">
-        <v>281.0329895019531</v>
+        <v>419.2177124023438</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         <v>363.3599853515625</v>
       </c>
       <c r="D11" t="n">
-        <v>281.0309753417969</v>
+        <v>415.6980895996094</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         <v>372.2400207519531</v>
       </c>
       <c r="D12" t="n">
-        <v>281.0276184082031</v>
+        <v>411.5213012695312</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +619,7 @@
         <v>350.1599426269531</v>
       </c>
       <c r="D13" t="n">
-        <v>281.0284118652344</v>
+        <v>393.0968933105469</v>
       </c>
     </row>
     <row r="14">
@@ -633,7 +633,7 @@
         <v>360.4800415039062</v>
       </c>
       <c r="D14" t="n">
-        <v>281.0270690917969</v>
+        <v>369.6758728027344</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         <v>363.3599853515625</v>
       </c>
       <c r="D15" t="n">
-        <v>281.0258483886719</v>
+        <v>347.0935668945312</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +661,7 @@
         <v>356.4000244140625</v>
       </c>
       <c r="D16" t="n">
-        <v>281.0253295898438</v>
+        <v>328.4844665527344</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         <v>337.6799621582031</v>
       </c>
       <c r="D17" t="n">
-        <v>281.0257263183594</v>
+        <v>311.862060546875</v>
       </c>
     </row>
     <row r="18">
@@ -689,7 +689,7 @@
         <v>301.6799621582031</v>
       </c>
       <c r="D18" t="n">
-        <v>281.0299072265625</v>
+        <v>296.8349304199219</v>
       </c>
     </row>
     <row r="19">
@@ -703,7 +703,7 @@
         <v>268.56005859375</v>
       </c>
       <c r="D19" t="n">
-        <v>281.0286865234375</v>
+        <v>282.5743408203125</v>
       </c>
     </row>
     <row r="20">
@@ -717,7 +717,7 @@
         <v>262.0800170898438</v>
       </c>
       <c r="D20" t="n">
-        <v>281.0184631347656</v>
+        <v>288.8166809082031</v>
       </c>
     </row>
     <row r="21">
@@ -731,7 +731,7 @@
         <v>268.56005859375</v>
       </c>
       <c r="D21" t="n">
-        <v>198.1138305664062</v>
+        <v>260.2913818359375</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         <v>250.7999725341797</v>
       </c>
       <c r="D22" t="n">
-        <v>198.1359558105469</v>
+        <v>248.5241088867188</v>
       </c>
     </row>
     <row r="23">
@@ -759,7 +759,7 @@
         <v>234.7199859619141</v>
       </c>
       <c r="D23" t="n">
-        <v>198.1344299316406</v>
+        <v>241.6534729003906</v>
       </c>
     </row>
     <row r="24">
@@ -773,7 +773,7 @@
         <v>228.47998046875</v>
       </c>
       <c r="D24" t="n">
-        <v>198.1311950683594</v>
+        <v>231.14306640625</v>
       </c>
     </row>
     <row r="25">
@@ -787,7 +787,7 @@
         <v>208.5600433349609</v>
       </c>
       <c r="D25" t="n">
-        <v>198.1267395019531</v>
+        <v>218.7992248535156</v>
       </c>
     </row>
     <row r="26">
@@ -801,7 +801,7 @@
         <v>186.9599609375</v>
       </c>
       <c r="D26" t="n">
-        <v>198.1263580322266</v>
+        <v>202.2541046142578</v>
       </c>
     </row>
     <row r="27">
@@ -815,7 +815,7 @@
         <v>157.1999816894531</v>
       </c>
       <c r="D27" t="n">
-        <v>198.1216125488281</v>
+        <v>179.4066162109375</v>
       </c>
     </row>
     <row r="28">
@@ -829,7 +829,7 @@
         <v>140.8800201416016</v>
       </c>
       <c r="D28" t="n">
-        <v>198.1193389892578</v>
+        <v>157.9451446533203</v>
       </c>
     </row>
     <row r="29">
@@ -843,7 +843,7 @@
         <v>132.7200164794922</v>
       </c>
       <c r="D29" t="n">
-        <v>198.1161956787109</v>
+        <v>138.2745513916016</v>
       </c>
     </row>
     <row r="30">
@@ -857,7 +857,7 @@
         <v>124.8000106811523</v>
       </c>
       <c r="D30" t="n">
-        <v>198.1160125732422</v>
+        <v>119.9610214233398</v>
       </c>
     </row>
     <row r="31">
@@ -871,7 +871,7 @@
         <v>110.1599807739258</v>
       </c>
       <c r="D31" t="n">
-        <v>198.1141052246094</v>
+        <v>106.976936340332</v>
       </c>
     </row>
     <row r="32">
@@ -885,7 +885,7 @@
         <v>111.8399810791016</v>
       </c>
       <c r="D32" t="n">
-        <v>198.1149597167969</v>
+        <v>97.85208129882812</v>
       </c>
     </row>
     <row r="33">
@@ -899,7 +899,7 @@
         <v>90.48000335693359</v>
       </c>
       <c r="D33" t="n">
-        <v>198.11572265625</v>
+        <v>88.65926361083984</v>
       </c>
     </row>
   </sheetData>
